--- a/students.xlsx
+++ b/students.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1975"/>
+  <dimension ref="A1:C2010"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30043,6 +30043,531 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1976">
+      <c r="A1976" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B1976" t="inlineStr">
+        <is>
+          <t>ACKAH SYLVESTER EBI</t>
+        </is>
+      </c>
+      <c r="C1976" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1977">
+      <c r="A1977" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B1977" t="inlineStr">
+        <is>
+          <t>AIDOO FRANCIS</t>
+        </is>
+      </c>
+      <c r="C1977" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1978">
+      <c r="A1978" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B1978" t="inlineStr">
+        <is>
+          <t>ANAANE RICHARD</t>
+        </is>
+      </c>
+      <c r="C1978" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1979">
+      <c r="A1979" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B1979" t="inlineStr">
+        <is>
+          <t>BAAH JESSICA</t>
+        </is>
+      </c>
+      <c r="C1979" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1980">
+      <c r="A1980" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B1980" t="inlineStr">
+        <is>
+          <t>OBENG EMMANUEL</t>
+        </is>
+      </c>
+      <c r="C1980" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1981">
+      <c r="A1981" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B1981" t="inlineStr">
+        <is>
+          <t>AKODACK IBRAHIM</t>
+        </is>
+      </c>
+      <c r="C1981" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1982">
+      <c r="A1982" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B1982" t="inlineStr">
+        <is>
+          <t>NTOWAH MAGDALENE</t>
+        </is>
+      </c>
+      <c r="C1982" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1983">
+      <c r="A1983" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B1983" t="inlineStr">
+        <is>
+          <t>BRAIMAH ALHASSAN</t>
+        </is>
+      </c>
+      <c r="C1983" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1984">
+      <c r="A1984" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B1984" t="inlineStr">
+        <is>
+          <t>BUKARI MUMUNI</t>
+        </is>
+      </c>
+      <c r="C1984" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1985">
+      <c r="A1985" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B1985" t="inlineStr">
+        <is>
+          <t>FEBRI AUGUSTINE</t>
+        </is>
+      </c>
+      <c r="C1985" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1986">
+      <c r="A1986" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B1986" t="inlineStr">
+        <is>
+          <t>SAANI KWAME</t>
+        </is>
+      </c>
+      <c r="C1986" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1987">
+      <c r="A1987" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B1987" t="inlineStr">
+        <is>
+          <t>SUMAILA SAMIRITU</t>
+        </is>
+      </c>
+      <c r="C1987" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1988">
+      <c r="A1988" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B1988" t="inlineStr">
+        <is>
+          <t>AKRUGU SARAH</t>
+        </is>
+      </c>
+      <c r="C1988" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1989">
+      <c r="A1989" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B1989" t="inlineStr">
+        <is>
+          <t>ISSAH RAHINATU</t>
+        </is>
+      </c>
+      <c r="C1989" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1990">
+      <c r="A1990" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B1990" t="inlineStr">
+        <is>
+          <t>KUSI THOMAS</t>
+        </is>
+      </c>
+      <c r="C1990" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1991">
+      <c r="A1991" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B1991" t="inlineStr">
+        <is>
+          <t>MORKLI DANIEL</t>
+        </is>
+      </c>
+      <c r="C1991" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1992">
+      <c r="A1992" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B1992" t="inlineStr">
+        <is>
+          <t>MENSAH MARGARET</t>
+        </is>
+      </c>
+      <c r="C1992" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1993">
+      <c r="A1993" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B1993" t="inlineStr">
+        <is>
+          <t>AFUKAAH SAMUEL</t>
+        </is>
+      </c>
+      <c r="C1993" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1994">
+      <c r="A1994" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B1994" t="inlineStr">
+        <is>
+          <t>MORO HANNAH</t>
+        </is>
+      </c>
+      <c r="C1994" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1995">
+      <c r="A1995" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B1995" t="inlineStr">
+        <is>
+          <t>AGBAGLO RICHARD</t>
+        </is>
+      </c>
+      <c r="C1995" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1996">
+      <c r="A1996" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B1996" t="inlineStr">
+        <is>
+          <t>AIDOO HANNAH</t>
+        </is>
+      </c>
+      <c r="C1996" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1997">
+      <c r="A1997" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B1997" t="inlineStr">
+        <is>
+          <t>BENIEL VINCENT</t>
+        </is>
+      </c>
+      <c r="C1997" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1998">
+      <c r="A1998" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B1998" t="inlineStr">
+        <is>
+          <t>ACKAH EMMANUEL</t>
+        </is>
+      </c>
+      <c r="C1998" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1999">
+      <c r="A1999" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B1999" t="inlineStr">
+        <is>
+          <t>MANU JULIANA</t>
+        </is>
+      </c>
+      <c r="C1999" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2000">
+      <c r="A2000" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B2000" t="inlineStr">
+        <is>
+          <t>QUASE ESTHER</t>
+        </is>
+      </c>
+      <c r="C2000" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2001">
+      <c r="A2001" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B2001" t="inlineStr">
+        <is>
+          <t>YAKUBU RAHINATU</t>
+        </is>
+      </c>
+      <c r="C2001" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2002">
+      <c r="A2002" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B2002" t="inlineStr">
+        <is>
+          <t>AMASAH EMMANUEL</t>
+        </is>
+      </c>
+      <c r="C2002" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2003">
+      <c r="A2003" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B2003" t="inlineStr">
+        <is>
+          <t>AMENYO HENRY GADMORE</t>
+        </is>
+      </c>
+      <c r="C2003" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2004">
+      <c r="A2004" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B2004" t="inlineStr">
+        <is>
+          <t>AMOAH GEORGINA</t>
+        </is>
+      </c>
+      <c r="C2004" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2005">
+      <c r="A2005" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B2005" t="inlineStr">
+        <is>
+          <t>AMOAH KELVIN ADADE</t>
+        </is>
+      </c>
+      <c r="C2005" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2006">
+      <c r="A2006" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B2006" t="inlineStr">
+        <is>
+          <t>AMONU PAOLINA</t>
+        </is>
+      </c>
+      <c r="C2006" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2007">
+      <c r="A2007" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B2007" t="inlineStr">
+        <is>
+          <t>GYAPONG PETER ADJEI</t>
+        </is>
+      </c>
+      <c r="C2007" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2008">
+      <c r="A2008" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B2008" t="inlineStr">
+        <is>
+          <t>KINTOH VANESSA AKUA</t>
+        </is>
+      </c>
+      <c r="C2008" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2009">
+      <c r="A2009" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B2009" t="inlineStr">
+        <is>
+          <t>MENSAH SILAS</t>
+        </is>
+      </c>
+      <c r="C2009" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2010">
+      <c r="A2010" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B2010" t="inlineStr">
+        <is>
+          <t>AWIDANI MOSES</t>
+        </is>
+      </c>
+      <c r="C2010" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
